--- a/dyno-docs-api/UI/Templates/places.xlsx
+++ b/dyno-docs-api/UI/Templates/places.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sgdp-dyno-docs\dyno-docs-temp\dyno-docs-api\UI\Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAC3D38-FB8B-454D-AB0E-C1828930BC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9707"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,21 +41,12 @@
     <t>City</t>
   </si>
   <si>
-    <t>Place Name</t>
-  </si>
-  <si>
     <t>Average Visit Duration</t>
   </si>
   <si>
-    <t>Touristy Description (comma separated string)</t>
-  </si>
-  <si>
     <t>Fun Fact</t>
   </si>
   <si>
-    <t>Pictures</t>
-  </si>
-  <si>
     <t>Central province</t>
   </si>
   <si>
@@ -243,19 +240,22 @@
   </si>
   <si>
     <t>Visitors can see elephants up close.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Images</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,353 +284,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -653,261 +316,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -917,68 +335,24 @@
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -989,11 +363,17 @@
     <xdr:ext cx="1638300" cy="1104900"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.jpg"/>
+        <xdr:cNvPr id="2" name="image1.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1021,11 +401,17 @@
     <xdr:ext cx="1619250" cy="828675"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image2.jpg"/>
+        <xdr:cNvPr id="3" name="image2.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1053,11 +439,17 @@
     <xdr:ext cx="1600200" cy="1085850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image3.jpg"/>
+        <xdr:cNvPr id="4" name="image3.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1085,11 +477,17 @@
     <xdr:ext cx="1647825" cy="923925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="image4.jpg"/>
+        <xdr:cNvPr id="5" name="image4.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1122,13 +520,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="galle-fort-1050x700-1"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="galle-fort-1050x700-1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1160,13 +564,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="temple"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="temple">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1198,13 +608,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="dambulla"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="dambulla">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1236,13 +652,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="nine arches"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="nine arches">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1274,13 +696,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="coconut"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="coconut">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1312,13 +740,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="river"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="river">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1350,13 +784,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="nine arches"/>
+        <xdr:cNvPr id="12" name="Picture 11" descr="nine arches">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1388,13 +828,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12" descr="badulla"/>
+        <xdr:cNvPr id="13" name="Picture 12" descr="badulla">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1426,13 +872,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13" descr="hambanthota"/>
+        <xdr:cNvPr id="14" name="Picture 13" descr="hambanthota">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1464,13 +916,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14" descr="greeen"/>
+        <xdr:cNvPr id="15" name="Picture 14" descr="greeen">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1502,13 +960,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15" descr="nuwara eliya"/>
+        <xdr:cNvPr id="16" name="Picture 15" descr="nuwara eliya">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1540,13 +1004,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16" descr="kegalles"/>
+        <xdr:cNvPr id="17" name="Picture 16" descr="kegalles">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1845,22 +1315,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.11111111111111" customWidth="1"/>
-    <col min="2" max="2" width="9.33333333333333" customWidth="1"/>
-    <col min="3" max="3" width="24.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="21.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="62.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="62.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="75.3425925925926" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="62.85546875" customWidth="1"/>
+    <col min="6" max="6" width="62.7109375" customWidth="1"/>
+    <col min="7" max="7" width="75.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1871,300 +1341,299 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="197.1" customHeight="1">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="197" customHeight="1" spans="1:7">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" ht="321" customHeight="1" spans="1:6">
+    <row r="3" spans="1:7" ht="321" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="302.10000000000002" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
         <v>18</v>
       </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="4" ht="302" customHeight="1" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="5" spans="1:7" ht="288" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
         <v>24</v>
       </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" ht="288" customHeight="1" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:7" ht="278.10000000000002" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="309" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="183" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="233.1" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="4"/>
     </row>
-    <row r="6" ht="278" customHeight="1" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
+    <row r="10" spans="1:7" ht="135" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="4"/>
     </row>
-    <row r="7" ht="309" customHeight="1" spans="1:7">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="4"/>
+    <row r="11" spans="1:7" ht="234" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="4"/>
     </row>
-    <row r="8" ht="183" customHeight="1" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="5"/>
+    <row r="12" spans="1:7" ht="227.1" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="4"/>
     </row>
-    <row r="9" ht="233" customHeight="1" spans="1:7">
-      <c r="A9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="5"/>
+    <row r="13" spans="1:7" ht="189.95" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="4"/>
     </row>
-    <row r="10" ht="135" customHeight="1" spans="1:7">
-      <c r="A10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4" t="s">
+    <row r="14" spans="1:7" ht="183" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" ht="234" customHeight="1" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" ht="227" customHeight="1" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" ht="190" customHeight="1" spans="1:7">
-      <c r="A13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" ht="183" customHeight="1" spans="1:7">
-      <c r="A14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F7" r:id="rId2" display="One of Sri Lanka’s most photographed coastal hills. (Wikipedia)" tooltip="https://en.wikipedia.org/wiki/Coconut_Tree_Hill?utm_source=chatgpt.com"/>
-    <hyperlink ref="F8" r:id="rId3" display="One of Sri Lanka’s finest ancient statues. (Wikipedia)" tooltip="https://en.wikipedia.org/wiki/Avukana_Buddha_statue?utm_source=chatgpt.com"/>
-    <hyperlink ref="F9" r:id="rId4" display="Named after mythical King Ravana. " tooltip="https://en.wikipedia.org/wiki/Ravana_Ella?utm_source=chatgpt.com"/>
-    <hyperlink ref="F10" r:id="rId5" display="Known for rising mist and spray. (Wikipedia)" tooltip="https://en.wikipedia.org/wiki/Dunhinda_Falls?utm_source=chatgpt.com"/>
-    <hyperlink ref="F11" r:id="rId6" display="One of Sri Lanka’s five major botanical gardens. (Wikipedia)" tooltip="https://en.wikipedia.org/wiki/Mirijjawila_Botanical_Garden?utm_source=chatgpt.com"/>
+    <hyperlink ref="F7" r:id="rId1" tooltip="https://en.wikipedia.org/wiki/Coconut_Tree_Hill?utm_source=chatgpt.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F8" r:id="rId2" tooltip="https://en.wikipedia.org/wiki/Avukana_Buddha_statue?utm_source=chatgpt.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F9" r:id="rId3" tooltip="https://en.wikipedia.org/wiki/Ravana_Ella?utm_source=chatgpt.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F10" r:id="rId4" tooltip="https://en.wikipedia.org/wiki/Dunhinda_Falls?utm_source=chatgpt.com" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F11" r:id="rId5" tooltip="https://en.wikipedia.org/wiki/Mirijjawila_Botanical_Garden?utm_source=chatgpt.com" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>